--- a/public/consultation_template_v2.xlsx
+++ b/public/consultation_template_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\satsu\kyojushien-saas\anshin-house-db\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB9B1CF-769B-4C9E-9144-BC252D2723B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFBA88D-9DB1-4A05-BA95-2A2B471387C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1138,14 +1138,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="15"/>
+      <sz val="14"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="15"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
@@ -1154,14 +1154,14 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="14"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="15"/>
+      <sz val="14"/>
       <color theme="1" tint="0.34998626667073579"/>
       <name val="游ゴシック"/>
       <family val="3"/>
@@ -1170,7 +1170,7 @@
     </font>
     <font>
       <u/>
-      <sz val="15"/>
+      <sz val="14"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1715,23 +1715,104 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1740,13 +1821,37 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1763,39 +1868,270 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1808,300 +2144,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -2111,6 +2159,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2119,57 +2170,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2556,381 +2556,381 @@
       <c r="AK1" s="3"/>
     </row>
     <row r="2" spans="1:37" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="81"/>
-      <c r="AB2" s="68" t="s">
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="AC2" s="68"/>
-      <c r="AD2" s="81" t="s">
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AE2" s="81"/>
-      <c r="AF2" s="68" t="s">
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="81" t="s">
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AI2" s="81"/>
-      <c r="AJ2" s="68" t="s">
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="68"/>
+      <c r="AK2" s="5"/>
     </row>
     <row r="3" spans="1:37" ht="29" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="82"/>
-      <c r="AB3" s="82"/>
-      <c r="AC3" s="82"/>
-      <c r="AD3" s="82"/>
-      <c r="AE3" s="82"/>
-      <c r="AF3" s="82"/>
-      <c r="AG3" s="82"/>
-      <c r="AH3" s="82"/>
-      <c r="AI3" s="82"/>
-      <c r="AJ3" s="82"/>
-      <c r="AK3" s="83"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
+      <c r="AI3" s="8"/>
+      <c r="AJ3" s="8"/>
+      <c r="AK3" s="9"/>
     </row>
     <row r="4" spans="1:37" ht="29" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="87"/>
-      <c r="S4" s="87"/>
-      <c r="T4" s="87"/>
-      <c r="U4" s="87"/>
-      <c r="V4" s="87"/>
-      <c r="W4" s="87"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="87"/>
-      <c r="AA4" s="87"/>
-      <c r="AB4" s="87"/>
-      <c r="AC4" s="87"/>
-      <c r="AD4" s="87"/>
-      <c r="AE4" s="87"/>
-      <c r="AF4" s="87"/>
-      <c r="AG4" s="87"/>
-      <c r="AH4" s="87"/>
-      <c r="AI4" s="87"/>
-      <c r="AJ4" s="87"/>
-      <c r="AK4" s="88"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="11"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="12"/>
     </row>
     <row r="5" spans="1:37" ht="29" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="87"/>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87"/>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="87"/>
-      <c r="U5" s="87"/>
-      <c r="V5" s="87"/>
-      <c r="W5" s="87"/>
-      <c r="X5" s="87"/>
-      <c r="Y5" s="87"/>
-      <c r="Z5" s="87"/>
-      <c r="AA5" s="87"/>
-      <c r="AB5" s="87"/>
-      <c r="AC5" s="87"/>
-      <c r="AD5" s="87"/>
-      <c r="AE5" s="87"/>
-      <c r="AF5" s="87"/>
-      <c r="AG5" s="87"/>
-      <c r="AH5" s="87"/>
-      <c r="AI5" s="87"/>
-      <c r="AJ5" s="87"/>
-      <c r="AK5" s="88"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="12"/>
     </row>
     <row r="6" spans="1:37" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="8" t="s">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="71" t="s">
+      <c r="Q6" s="16"/>
+      <c r="R6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="S6" s="72"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="75" t="s">
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="78" t="s">
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="Y6" s="72"/>
-      <c r="Z6" s="79"/>
-      <c r="AA6" s="89" t="s">
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="AB6" s="47"/>
-      <c r="AC6" s="47"/>
-      <c r="AD6" s="47"/>
-      <c r="AE6" s="47"/>
-      <c r="AF6" s="47"/>
-      <c r="AG6" s="47"/>
-      <c r="AH6" s="47"/>
-      <c r="AI6" s="47"/>
-      <c r="AJ6" s="47"/>
-      <c r="AK6" s="48"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24"/>
+      <c r="AI6" s="24"/>
+      <c r="AJ6" s="24"/>
+      <c r="AK6" s="25"/>
     </row>
     <row r="7" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="86" t="s">
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q7" s="86"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="74"/>
-      <c r="T7" s="74"/>
-      <c r="U7" s="76"/>
-      <c r="V7" s="77"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="73"/>
-      <c r="Y7" s="74"/>
-      <c r="Z7" s="80"/>
-      <c r="AA7" s="90"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="91"/>
-      <c r="AJ7" s="91"/>
-      <c r="AK7" s="92"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="36"/>
+      <c r="AE7" s="36"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="36"/>
+      <c r="AH7" s="36"/>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="36"/>
+      <c r="AK7" s="37"/>
     </row>
     <row r="8" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="63" t="s">
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="63"/>
-      <c r="W8" s="63"/>
-      <c r="X8" s="63"/>
-      <c r="Y8" s="63"/>
-      <c r="Z8" s="63"/>
-      <c r="AA8" s="63"/>
-      <c r="AB8" s="63"/>
-      <c r="AC8" s="63"/>
-      <c r="AD8" s="63"/>
-      <c r="AE8" s="63"/>
-      <c r="AF8" s="63"/>
-      <c r="AG8" s="63"/>
-      <c r="AH8" s="63"/>
-      <c r="AI8" s="63"/>
-      <c r="AJ8" s="63"/>
-      <c r="AK8" s="64"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="41"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="41"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="41"/>
+      <c r="AB8" s="41"/>
+      <c r="AC8" s="41"/>
+      <c r="AD8" s="41"/>
+      <c r="AE8" s="41"/>
+      <c r="AF8" s="41"/>
+      <c r="AG8" s="41"/>
+      <c r="AH8" s="41"/>
+      <c r="AI8" s="41"/>
+      <c r="AJ8" s="41"/>
+      <c r="AK8" s="42"/>
     </row>
     <row r="9" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="57"/>
-      <c r="P9" s="57"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="59" t="s">
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="S9" s="60"/>
-      <c r="T9" s="61"/>
-      <c r="U9" s="56" t="s">
+      <c r="S9" s="46"/>
+      <c r="T9" s="47"/>
+      <c r="U9" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="V9" s="57"/>
-      <c r="W9" s="57"/>
-      <c r="X9" s="57"/>
-      <c r="Y9" s="57"/>
-      <c r="Z9" s="57"/>
-      <c r="AA9" s="57"/>
-      <c r="AB9" s="57"/>
-      <c r="AC9" s="57"/>
-      <c r="AD9" s="57"/>
-      <c r="AE9" s="57"/>
-      <c r="AF9" s="57"/>
-      <c r="AG9" s="57"/>
-      <c r="AH9" s="57"/>
-      <c r="AI9" s="57"/>
-      <c r="AJ9" s="57"/>
-      <c r="AK9" s="58"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="40"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="40"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="40"/>
+      <c r="AG9" s="40"/>
+      <c r="AH9" s="40"/>
+      <c r="AI9" s="40"/>
+      <c r="AJ9" s="40"/>
+      <c r="AK9" s="44"/>
     </row>
     <row r="10" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="48" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="49" t="s">
@@ -2938,343 +2938,343 @@
       </c>
       <c r="C10" s="50"/>
       <c r="D10" s="50"/>
-      <c r="E10" s="47" t="s">
+      <c r="E10" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="62"/>
-      <c r="G10" s="16" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="H10" s="47" t="s">
+      <c r="H10" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="16" t="s">
+      <c r="I10" s="20"/>
+      <c r="J10" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L10" s="62"/>
-      <c r="M10" s="16" t="s">
+      <c r="L10" s="20"/>
+      <c r="M10" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="17"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="19" t="s">
+      <c r="N10" s="52"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="Q10" s="47" t="s">
+      <c r="Q10" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="R10" s="62"/>
-      <c r="S10" s="20" t="s">
+      <c r="R10" s="20"/>
+      <c r="S10" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="T10" s="20"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="44" t="s">
+      <c r="T10" s="55"/>
+      <c r="U10" s="56"/>
+      <c r="V10" s="57" t="s">
         <v>170</v>
       </c>
-      <c r="W10" s="45"/>
-      <c r="X10" s="46"/>
-      <c r="Y10" s="65" t="s">
+      <c r="W10" s="58"/>
+      <c r="X10" s="59"/>
+      <c r="Y10" s="60" t="s">
         <v>171</v>
       </c>
-      <c r="Z10" s="66"/>
-      <c r="AA10" s="66"/>
-      <c r="AB10" s="66"/>
-      <c r="AC10" s="66"/>
-      <c r="AD10" s="66"/>
-      <c r="AE10" s="66"/>
-      <c r="AF10" s="66"/>
-      <c r="AG10" s="66"/>
-      <c r="AH10" s="66"/>
-      <c r="AI10" s="66"/>
-      <c r="AJ10" s="66"/>
-      <c r="AK10" s="67"/>
+      <c r="Z10" s="61"/>
+      <c r="AA10" s="61"/>
+      <c r="AB10" s="61"/>
+      <c r="AC10" s="61"/>
+      <c r="AD10" s="61"/>
+      <c r="AE10" s="61"/>
+      <c r="AF10" s="61"/>
+      <c r="AG10" s="61"/>
+      <c r="AH10" s="61"/>
+      <c r="AI10" s="61"/>
+      <c r="AJ10" s="61"/>
+      <c r="AK10" s="62"/>
     </row>
     <row r="11" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="94"/>
-      <c r="P11" s="94"/>
-      <c r="Q11" s="94"/>
-      <c r="R11" s="94"/>
-      <c r="S11" s="94"/>
-      <c r="T11" s="94"/>
-      <c r="U11" s="94"/>
-      <c r="V11" s="94"/>
-      <c r="W11" s="94"/>
-      <c r="X11" s="94"/>
-      <c r="Y11" s="94"/>
-      <c r="Z11" s="94"/>
-      <c r="AA11" s="94"/>
-      <c r="AB11" s="94"/>
-      <c r="AC11" s="94"/>
-      <c r="AD11" s="94"/>
-      <c r="AE11" s="94"/>
-      <c r="AF11" s="94"/>
-      <c r="AG11" s="94"/>
-      <c r="AH11" s="94"/>
-      <c r="AI11" s="94"/>
-      <c r="AJ11" s="94"/>
-      <c r="AK11" s="95"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
+      <c r="R11" s="64"/>
+      <c r="S11" s="64"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="64"/>
+      <c r="AA11" s="64"/>
+      <c r="AB11" s="64"/>
+      <c r="AC11" s="64"/>
+      <c r="AD11" s="64"/>
+      <c r="AE11" s="64"/>
+      <c r="AF11" s="64"/>
+      <c r="AG11" s="64"/>
+      <c r="AH11" s="64"/>
+      <c r="AI11" s="64"/>
+      <c r="AJ11" s="64"/>
+      <c r="AK11" s="65"/>
     </row>
     <row r="12" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="73"/>
-      <c r="B12" s="76" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77" t="s">
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="M12" s="77"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="91" t="s">
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="Q12" s="91"/>
-      <c r="R12" s="91"/>
-      <c r="S12" s="91"/>
-      <c r="T12" s="91"/>
-      <c r="U12" s="91"/>
-      <c r="V12" s="91"/>
-      <c r="W12" s="91"/>
-      <c r="X12" s="77" t="s">
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="Y12" s="77"/>
-      <c r="Z12" s="77"/>
-      <c r="AA12" s="77"/>
-      <c r="AB12" s="77" t="s">
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="33"/>
+      <c r="AB12" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="AC12" s="77"/>
-      <c r="AD12" s="77"/>
-      <c r="AE12" s="77"/>
-      <c r="AF12" s="77"/>
-      <c r="AG12" s="77"/>
-      <c r="AH12" s="77"/>
-      <c r="AI12" s="77" t="s">
+      <c r="AC12" s="33"/>
+      <c r="AD12" s="33"/>
+      <c r="AE12" s="33"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="33"/>
+      <c r="AH12" s="33"/>
+      <c r="AI12" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="AJ12" s="77"/>
-      <c r="AK12" s="96"/>
+      <c r="AJ12" s="33"/>
+      <c r="AK12" s="66"/>
     </row>
     <row r="13" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="103" t="s">
+      <c r="B13" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="104"/>
-      <c r="P13" s="104"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="104"/>
-      <c r="S13" s="104"/>
-      <c r="T13" s="104"/>
-      <c r="U13" s="104"/>
-      <c r="V13" s="104"/>
-      <c r="W13" s="104"/>
-      <c r="X13" s="104"/>
-      <c r="Y13" s="104"/>
-      <c r="Z13" s="104"/>
-      <c r="AA13" s="104"/>
-      <c r="AB13" s="104"/>
-      <c r="AC13" s="104"/>
-      <c r="AD13" s="104"/>
-      <c r="AE13" s="104"/>
-      <c r="AF13" s="104"/>
-      <c r="AG13" s="104"/>
-      <c r="AH13" s="104"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="104"/>
-      <c r="AK13" s="105"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="68"/>
+      <c r="T13" s="68"/>
+      <c r="U13" s="68"/>
+      <c r="V13" s="68"/>
+      <c r="W13" s="68"/>
+      <c r="X13" s="68"/>
+      <c r="Y13" s="68"/>
+      <c r="Z13" s="68"/>
+      <c r="AA13" s="68"/>
+      <c r="AB13" s="68"/>
+      <c r="AC13" s="68"/>
+      <c r="AD13" s="68"/>
+      <c r="AE13" s="68"/>
+      <c r="AF13" s="68"/>
+      <c r="AG13" s="68"/>
+      <c r="AH13" s="68"/>
+      <c r="AI13" s="68"/>
+      <c r="AJ13" s="68"/>
+      <c r="AK13" s="69"/>
     </row>
     <row r="14" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="97"/>
-      <c r="B14" s="59" t="s">
+      <c r="A14" s="70"/>
+      <c r="B14" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="99" t="s">
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="71" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="100"/>
-      <c r="K14" s="100"/>
-      <c r="L14" s="100"/>
-      <c r="M14" s="100"/>
-      <c r="N14" s="100"/>
-      <c r="O14" s="100"/>
-      <c r="P14" s="100"/>
-      <c r="Q14" s="100"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="100"/>
-      <c r="T14" s="100"/>
-      <c r="U14" s="100"/>
-      <c r="V14" s="100"/>
-      <c r="W14" s="100"/>
-      <c r="X14" s="100"/>
-      <c r="Y14" s="100"/>
-      <c r="Z14" s="100"/>
-      <c r="AA14" s="100"/>
-      <c r="AB14" s="100"/>
-      <c r="AC14" s="100"/>
-      <c r="AD14" s="100"/>
-      <c r="AE14" s="100"/>
-      <c r="AF14" s="100"/>
-      <c r="AG14" s="100"/>
-      <c r="AH14" s="100"/>
-      <c r="AI14" s="100"/>
-      <c r="AJ14" s="100"/>
-      <c r="AK14" s="101"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="72"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="72"/>
+      <c r="AB14" s="72"/>
+      <c r="AC14" s="72"/>
+      <c r="AD14" s="72"/>
+      <c r="AE14" s="72"/>
+      <c r="AF14" s="72"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="72"/>
+      <c r="AI14" s="72"/>
+      <c r="AJ14" s="72"/>
+      <c r="AK14" s="73"/>
     </row>
     <row r="15" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="98"/>
-      <c r="B15" s="73" t="s">
+      <c r="A15" s="74"/>
+      <c r="B15" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="102" t="s">
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="75" t="s">
         <v>126</v>
       </c>
-      <c r="J15" s="100"/>
-      <c r="K15" s="100"/>
-      <c r="L15" s="100"/>
-      <c r="M15" s="100"/>
-      <c r="N15" s="100"/>
-      <c r="O15" s="100"/>
-      <c r="P15" s="100"/>
-      <c r="Q15" s="100"/>
-      <c r="R15" s="100"/>
-      <c r="S15" s="100"/>
-      <c r="T15" s="100"/>
-      <c r="U15" s="100"/>
-      <c r="V15" s="100"/>
-      <c r="W15" s="100"/>
-      <c r="X15" s="100"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="59" t="s">
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="72"/>
+      <c r="X15" s="72"/>
+      <c r="Y15" s="73"/>
+      <c r="Z15" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="AA15" s="60"/>
-      <c r="AB15" s="60"/>
-      <c r="AC15" s="61"/>
-      <c r="AD15" s="56" t="s">
+      <c r="AA15" s="46"/>
+      <c r="AB15" s="46"/>
+      <c r="AC15" s="47"/>
+      <c r="AD15" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="AE15" s="57"/>
-      <c r="AF15" s="57"/>
-      <c r="AG15" s="57"/>
-      <c r="AH15" s="57"/>
-      <c r="AI15" s="57"/>
-      <c r="AJ15" s="57"/>
-      <c r="AK15" s="58"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="40"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="44"/>
     </row>
     <row r="16" spans="1:37" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="113" t="s">
+      <c r="B16" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="114"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="114"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="114"/>
-      <c r="M16" s="114"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="114"/>
-      <c r="R16" s="114"/>
-      <c r="S16" s="114"/>
-      <c r="T16" s="114"/>
-      <c r="U16" s="114"/>
-      <c r="V16" s="114"/>
-      <c r="W16" s="114"/>
-      <c r="X16" s="114"/>
-      <c r="Y16" s="114"/>
-      <c r="Z16" s="114"/>
-      <c r="AA16" s="114"/>
-      <c r="AB16" s="114"/>
-      <c r="AC16" s="114"/>
-      <c r="AD16" s="114"/>
-      <c r="AE16" s="114"/>
-      <c r="AF16" s="114"/>
-      <c r="AG16" s="114"/>
-      <c r="AH16" s="114"/>
-      <c r="AI16" s="114"/>
-      <c r="AJ16" s="114"/>
-      <c r="AK16" s="115"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="77"/>
+      <c r="S16" s="77"/>
+      <c r="T16" s="77"/>
+      <c r="U16" s="77"/>
+      <c r="V16" s="77"/>
+      <c r="W16" s="77"/>
+      <c r="X16" s="77"/>
+      <c r="Y16" s="77"/>
+      <c r="Z16" s="77"/>
+      <c r="AA16" s="77"/>
+      <c r="AB16" s="77"/>
+      <c r="AC16" s="77"/>
+      <c r="AD16" s="77"/>
+      <c r="AE16" s="77"/>
+      <c r="AF16" s="77"/>
+      <c r="AG16" s="77"/>
+      <c r="AH16" s="77"/>
+      <c r="AI16" s="77"/>
+      <c r="AJ16" s="77"/>
+      <c r="AK16" s="78"/>
     </row>
     <row r="17" spans="1:37" ht="44" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="46"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="59"/>
       <c r="G17" s="49" t="s">
         <v>104</v>
       </c>
@@ -3285,7 +3285,7 @@
       <c r="L17" s="50"/>
       <c r="M17" s="50"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="47"/>
+      <c r="O17" s="24"/>
       <c r="P17" s="50"/>
       <c r="Q17" s="50"/>
       <c r="R17" s="50"/>
@@ -3295,86 +3295,86 @@
       <c r="V17" s="50"/>
       <c r="W17" s="50"/>
       <c r="X17" s="50"/>
-      <c r="Y17" s="51"/>
-      <c r="Z17" s="71" t="s">
+      <c r="Y17" s="80"/>
+      <c r="Z17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AA17" s="72"/>
-      <c r="AB17" s="72"/>
-      <c r="AC17" s="79"/>
-      <c r="AD17" s="56" t="s">
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="AE17" s="57"/>
-      <c r="AF17" s="57"/>
-      <c r="AG17" s="57"/>
-      <c r="AH17" s="57"/>
-      <c r="AI17" s="57"/>
-      <c r="AJ17" s="57"/>
-      <c r="AK17" s="58"/>
+      <c r="AE17" s="40"/>
+      <c r="AF17" s="40"/>
+      <c r="AG17" s="40"/>
+      <c r="AH17" s="40"/>
+      <c r="AI17" s="40"/>
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="44"/>
     </row>
     <row r="18" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="46"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="59"/>
       <c r="G18" s="49" t="s">
         <v>135</v>
       </c>
       <c r="H18" s="50"/>
       <c r="I18" s="50"/>
-      <c r="J18" s="116" t="s">
+      <c r="J18" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="K18" s="116"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="116"/>
-      <c r="O18" s="89" t="s">
+      <c r="K18" s="82"/>
+      <c r="L18" s="82"/>
+      <c r="M18" s="82"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="44" t="s">
+      <c r="P18" s="25"/>
+      <c r="Q18" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="52" t="s">
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="59"/>
+      <c r="U18" s="83" t="s">
         <v>139</v>
       </c>
-      <c r="V18" s="53"/>
-      <c r="W18" s="53"/>
-      <c r="X18" s="53"/>
-      <c r="Y18" s="53"/>
-      <c r="Z18" s="53"/>
-      <c r="AA18" s="53"/>
-      <c r="AB18" s="53"/>
-      <c r="AC18" s="53"/>
-      <c r="AD18" s="53"/>
-      <c r="AE18" s="53"/>
-      <c r="AF18" s="53"/>
-      <c r="AG18" s="53"/>
-      <c r="AH18" s="53"/>
-      <c r="AI18" s="53"/>
-      <c r="AJ18" s="53"/>
-      <c r="AK18" s="54"/>
+      <c r="V18" s="84"/>
+      <c r="W18" s="84"/>
+      <c r="X18" s="84"/>
+      <c r="Y18" s="84"/>
+      <c r="Z18" s="84"/>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="84"/>
+      <c r="AC18" s="84"/>
+      <c r="AD18" s="84"/>
+      <c r="AE18" s="84"/>
+      <c r="AF18" s="84"/>
+      <c r="AG18" s="84"/>
+      <c r="AH18" s="84"/>
+      <c r="AI18" s="84"/>
+      <c r="AJ18" s="84"/>
+      <c r="AK18" s="85"/>
     </row>
     <row r="19" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="42"/>
-      <c r="B19" s="44" t="s">
+      <c r="A19" s="86"/>
+      <c r="B19" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="46"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="59"/>
       <c r="G19" s="49" t="s">
         <v>141</v>
       </c>
@@ -3384,984 +3384,984 @@
       <c r="K19" s="50"/>
       <c r="L19" s="50"/>
       <c r="M19" s="50"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="44" t="s">
+      <c r="N19" s="80"/>
+      <c r="O19" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="52" t="s">
+      <c r="P19" s="59"/>
+      <c r="Q19" s="83" t="s">
         <v>143</v>
       </c>
-      <c r="R19" s="53"/>
-      <c r="S19" s="53"/>
-      <c r="T19" s="53"/>
-      <c r="U19" s="53"/>
-      <c r="V19" s="53"/>
-      <c r="W19" s="53"/>
-      <c r="X19" s="53"/>
-      <c r="Y19" s="53"/>
-      <c r="Z19" s="53"/>
-      <c r="AA19" s="53"/>
-      <c r="AB19" s="53"/>
-      <c r="AC19" s="53"/>
-      <c r="AD19" s="53"/>
-      <c r="AE19" s="53"/>
-      <c r="AF19" s="53"/>
-      <c r="AG19" s="53"/>
-      <c r="AH19" s="53"/>
-      <c r="AI19" s="53"/>
-      <c r="AJ19" s="53"/>
-      <c r="AK19" s="54"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="84"/>
+      <c r="AK19" s="85"/>
     </row>
     <row r="20" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44" t="s">
+      <c r="A20" s="87"/>
+      <c r="B20" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="52" t="s">
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="83" t="s">
         <v>166</v>
       </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="53"/>
-      <c r="U20" s="53"/>
-      <c r="V20" s="53"/>
-      <c r="W20" s="53"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="53"/>
-      <c r="AA20" s="53"/>
-      <c r="AB20" s="53"/>
-      <c r="AC20" s="53"/>
-      <c r="AD20" s="53"/>
-      <c r="AE20" s="53"/>
-      <c r="AF20" s="53"/>
-      <c r="AG20" s="53"/>
-      <c r="AH20" s="53"/>
-      <c r="AI20" s="53"/>
-      <c r="AJ20" s="53"/>
-      <c r="AK20" s="54"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="88"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="84"/>
+      <c r="P20" s="84"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="84"/>
+      <c r="S20" s="84"/>
+      <c r="T20" s="84"/>
+      <c r="U20" s="84"/>
+      <c r="V20" s="84"/>
+      <c r="W20" s="84"/>
+      <c r="X20" s="84"/>
+      <c r="Y20" s="84"/>
+      <c r="Z20" s="84"/>
+      <c r="AA20" s="84"/>
+      <c r="AB20" s="84"/>
+      <c r="AC20" s="84"/>
+      <c r="AD20" s="84"/>
+      <c r="AE20" s="84"/>
+      <c r="AF20" s="84"/>
+      <c r="AG20" s="84"/>
+      <c r="AH20" s="84"/>
+      <c r="AI20" s="84"/>
+      <c r="AJ20" s="84"/>
+      <c r="AK20" s="85"/>
     </row>
     <row r="21" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="106" t="s">
+      <c r="A21" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="56" t="s">
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="22" t="s">
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="O21" s="59" t="s">
+      <c r="O21" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="57" t="s">
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="U21" s="57"/>
-      <c r="V21" s="57"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="57"/>
-      <c r="Y21" s="40" t="s">
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="40"/>
+      <c r="Y21" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="Z21" s="110" t="s">
+      <c r="Z21" s="92" t="s">
         <v>173</v>
       </c>
-      <c r="AA21" s="111"/>
-      <c r="AB21" s="111"/>
-      <c r="AC21" s="111"/>
-      <c r="AD21" s="111"/>
-      <c r="AE21" s="112"/>
-      <c r="AF21" s="108" t="s">
+      <c r="AA21" s="93"/>
+      <c r="AB21" s="93"/>
+      <c r="AC21" s="93"/>
+      <c r="AD21" s="93"/>
+      <c r="AE21" s="94"/>
+      <c r="AF21" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="AG21" s="108"/>
-      <c r="AH21" s="108"/>
-      <c r="AI21" s="108"/>
-      <c r="AJ21" s="108"/>
-      <c r="AK21" s="39" t="s">
+      <c r="AG21" s="95"/>
+      <c r="AH21" s="95"/>
+      <c r="AI21" s="95"/>
+      <c r="AJ21" s="95"/>
+      <c r="AK21" s="96" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="73"/>
-      <c r="B22" s="59" t="s">
+      <c r="A22" s="30"/>
+      <c r="B22" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="107" t="s">
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="97" t="s">
         <v>69</v>
       </c>
-      <c r="H22" s="108"/>
-      <c r="I22" s="108"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="108"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="73" t="s">
+      <c r="H22" s="95"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="95"/>
+      <c r="K22" s="95"/>
+      <c r="L22" s="98"/>
+      <c r="M22" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="N22" s="60"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="56" t="s">
+      <c r="N22" s="46"/>
+      <c r="O22" s="46"/>
+      <c r="P22" s="47"/>
+      <c r="Q22" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="R22" s="57"/>
-      <c r="S22" s="57"/>
-      <c r="T22" s="57"/>
-      <c r="U22" s="57"/>
-      <c r="V22" s="57"/>
-      <c r="W22" s="57"/>
-      <c r="X22" s="57"/>
-      <c r="Y22" s="57"/>
-      <c r="Z22" s="57"/>
-      <c r="AA22" s="57"/>
-      <c r="AB22" s="57"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="37" t="s">
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="X22" s="40"/>
+      <c r="Y22" s="40"/>
+      <c r="Z22" s="40"/>
+      <c r="AA22" s="40"/>
+      <c r="AB22" s="40"/>
+      <c r="AC22" s="38"/>
+      <c r="AD22" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="AE22" s="38"/>
-      <c r="AF22" s="57" t="s">
+      <c r="AE22" s="100"/>
+      <c r="AF22" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="AG22" s="57"/>
-      <c r="AH22" s="57"/>
-      <c r="AI22" s="57"/>
-      <c r="AJ22" s="57"/>
-      <c r="AK22" s="39" t="s">
+      <c r="AG22" s="40"/>
+      <c r="AH22" s="40"/>
+      <c r="AI22" s="40"/>
+      <c r="AJ22" s="40"/>
+      <c r="AK22" s="96" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="71" t="s">
+      <c r="A23" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="117" t="s">
+      <c r="B23" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="126" t="s">
+      <c r="C23" s="102"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="127"/>
-      <c r="K23" s="127"/>
-      <c r="L23" s="127"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="127"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="127"/>
-      <c r="Q23" s="127"/>
-      <c r="R23" s="127"/>
-      <c r="S23" s="127"/>
-      <c r="T23" s="127"/>
-      <c r="U23" s="127"/>
-      <c r="V23" s="127"/>
-      <c r="W23" s="127"/>
-      <c r="X23" s="127"/>
-      <c r="Y23" s="128"/>
-      <c r="Z23" s="127"/>
-      <c r="AA23" s="127"/>
-      <c r="AB23" s="127"/>
-      <c r="AC23" s="127"/>
-      <c r="AD23" s="127"/>
-      <c r="AE23" s="127"/>
-      <c r="AF23" s="127"/>
-      <c r="AG23" s="127"/>
-      <c r="AH23" s="127"/>
-      <c r="AI23" s="127"/>
-      <c r="AJ23" s="127"/>
-      <c r="AK23" s="129"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="105"/>
+      <c r="P23" s="105"/>
+      <c r="Q23" s="105"/>
+      <c r="R23" s="105"/>
+      <c r="S23" s="105"/>
+      <c r="T23" s="105"/>
+      <c r="U23" s="105"/>
+      <c r="V23" s="105"/>
+      <c r="W23" s="105"/>
+      <c r="X23" s="105"/>
+      <c r="Y23" s="106"/>
+      <c r="Z23" s="105"/>
+      <c r="AA23" s="105"/>
+      <c r="AB23" s="105"/>
+      <c r="AC23" s="105"/>
+      <c r="AD23" s="105"/>
+      <c r="AE23" s="105"/>
+      <c r="AF23" s="105"/>
+      <c r="AG23" s="105"/>
+      <c r="AH23" s="105"/>
+      <c r="AI23" s="105"/>
+      <c r="AJ23" s="105"/>
+      <c r="AK23" s="107"/>
     </row>
     <row r="24" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="106"/>
-      <c r="B24" s="120" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="121"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="23" t="s">
+      <c r="C24" s="109"/>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="111" t="s">
         <v>117</v>
       </c>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="130" t="s">
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="113" t="s">
         <v>118</v>
       </c>
-      <c r="K24" s="130"/>
-      <c r="L24" s="130"/>
-      <c r="M24" s="130"/>
-      <c r="N24" s="130"/>
-      <c r="O24" s="130"/>
-      <c r="P24" s="130"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="25" t="s">
+      <c r="K24" s="113"/>
+      <c r="L24" s="113"/>
+      <c r="M24" s="113"/>
+      <c r="N24" s="113"/>
+      <c r="O24" s="113"/>
+      <c r="P24" s="113"/>
+      <c r="Q24" s="112"/>
+      <c r="R24" s="114" t="s">
         <v>119</v>
       </c>
-      <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="130" t="s">
+      <c r="S24" s="112"/>
+      <c r="T24" s="112"/>
+      <c r="U24" s="112"/>
+      <c r="V24" s="113" t="s">
         <v>120</v>
       </c>
-      <c r="W24" s="130"/>
-      <c r="X24" s="130"/>
-      <c r="Y24" s="130"/>
-      <c r="Z24" s="130"/>
-      <c r="AA24" s="130"/>
-      <c r="AB24" s="130"/>
-      <c r="AC24" s="24"/>
-      <c r="AD24" s="25" t="s">
+      <c r="W24" s="113"/>
+      <c r="X24" s="113"/>
+      <c r="Y24" s="113"/>
+      <c r="Z24" s="113"/>
+      <c r="AA24" s="113"/>
+      <c r="AB24" s="113"/>
+      <c r="AC24" s="112"/>
+      <c r="AD24" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="AE24" s="24"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="24"/>
-      <c r="AH24" s="24"/>
-      <c r="AI24" s="24"/>
-      <c r="AJ24" s="130" t="s">
+      <c r="AE24" s="112"/>
+      <c r="AF24" s="112"/>
+      <c r="AG24" s="112"/>
+      <c r="AH24" s="112"/>
+      <c r="AI24" s="112"/>
+      <c r="AJ24" s="113" t="s">
         <v>122</v>
       </c>
-      <c r="AK24" s="131"/>
+      <c r="AK24" s="115"/>
     </row>
     <row r="25" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="106"/>
-      <c r="B25" s="120" t="s">
+      <c r="A25" s="89"/>
+      <c r="B25" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="122"/>
-      <c r="G25" s="125" t="s">
+      <c r="C25" s="109"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="123"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="123"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="123"/>
-      <c r="M25" s="123"/>
-      <c r="N25" s="123"/>
-      <c r="O25" s="123"/>
-      <c r="P25" s="123"/>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="123" t="s">
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="117"/>
+      <c r="L25" s="117"/>
+      <c r="M25" s="117"/>
+      <c r="N25" s="117"/>
+      <c r="O25" s="117"/>
+      <c r="P25" s="117"/>
+      <c r="Q25" s="118"/>
+      <c r="R25" s="118"/>
+      <c r="S25" s="117" t="s">
         <v>108</v>
       </c>
-      <c r="T25" s="123"/>
-      <c r="U25" s="123"/>
-      <c r="V25" s="123"/>
-      <c r="W25" s="123"/>
-      <c r="X25" s="123"/>
-      <c r="Y25" s="123"/>
-      <c r="Z25" s="123"/>
-      <c r="AA25" s="123"/>
-      <c r="AB25" s="123"/>
-      <c r="AC25" s="123"/>
-      <c r="AD25" s="123"/>
-      <c r="AE25" s="123"/>
-      <c r="AF25" s="123"/>
-      <c r="AG25" s="123"/>
-      <c r="AH25" s="123"/>
-      <c r="AI25" s="123"/>
-      <c r="AJ25" s="123"/>
-      <c r="AK25" s="124"/>
+      <c r="T25" s="117"/>
+      <c r="U25" s="117"/>
+      <c r="V25" s="117"/>
+      <c r="W25" s="117"/>
+      <c r="X25" s="117"/>
+      <c r="Y25" s="117"/>
+      <c r="Z25" s="117"/>
+      <c r="AA25" s="117"/>
+      <c r="AB25" s="117"/>
+      <c r="AC25" s="117"/>
+      <c r="AD25" s="117"/>
+      <c r="AE25" s="117"/>
+      <c r="AF25" s="117"/>
+      <c r="AG25" s="117"/>
+      <c r="AH25" s="117"/>
+      <c r="AI25" s="117"/>
+      <c r="AJ25" s="117"/>
+      <c r="AK25" s="119"/>
     </row>
     <row r="26" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="106"/>
-      <c r="B26" s="120" t="s">
+      <c r="A26" s="89"/>
+      <c r="B26" s="108" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="125" t="s">
+      <c r="C26" s="109"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="116" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="123"/>
-      <c r="K26" s="123"/>
-      <c r="L26" s="123"/>
-      <c r="M26" s="123"/>
-      <c r="N26" s="123"/>
-      <c r="O26" s="123"/>
-      <c r="P26" s="123"/>
-      <c r="Q26" s="123"/>
-      <c r="R26" s="123"/>
-      <c r="S26" s="123"/>
-      <c r="T26" s="123"/>
-      <c r="U26" s="123"/>
-      <c r="V26" s="123"/>
-      <c r="W26" s="123"/>
-      <c r="X26" s="123"/>
-      <c r="Y26" s="123"/>
-      <c r="Z26" s="123"/>
-      <c r="AA26" s="123"/>
-      <c r="AB26" s="123"/>
-      <c r="AC26" s="123"/>
-      <c r="AD26" s="123"/>
-      <c r="AE26" s="123"/>
-      <c r="AF26" s="123"/>
-      <c r="AG26" s="123"/>
-      <c r="AH26" s="123"/>
-      <c r="AI26" s="123"/>
-      <c r="AJ26" s="123"/>
-      <c r="AK26" s="124"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="117"/>
+      <c r="O26" s="117"/>
+      <c r="P26" s="117"/>
+      <c r="Q26" s="117"/>
+      <c r="R26" s="117"/>
+      <c r="S26" s="117"/>
+      <c r="T26" s="117"/>
+      <c r="U26" s="117"/>
+      <c r="V26" s="117"/>
+      <c r="W26" s="117"/>
+      <c r="X26" s="117"/>
+      <c r="Y26" s="117"/>
+      <c r="Z26" s="117"/>
+      <c r="AA26" s="117"/>
+      <c r="AB26" s="117"/>
+      <c r="AC26" s="117"/>
+      <c r="AD26" s="117"/>
+      <c r="AE26" s="117"/>
+      <c r="AF26" s="117"/>
+      <c r="AG26" s="117"/>
+      <c r="AH26" s="117"/>
+      <c r="AI26" s="117"/>
+      <c r="AJ26" s="117"/>
+      <c r="AK26" s="119"/>
     </row>
     <row r="27" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="106"/>
-      <c r="B27" s="120" t="s">
+      <c r="A27" s="89"/>
+      <c r="B27" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="121"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="125" t="s">
+      <c r="C27" s="109"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="H27" s="123"/>
-      <c r="I27" s="123"/>
-      <c r="J27" s="123"/>
-      <c r="K27" s="123"/>
-      <c r="L27" s="123"/>
-      <c r="M27" s="123"/>
-      <c r="N27" s="123"/>
-      <c r="O27" s="123"/>
-      <c r="P27" s="123"/>
-      <c r="Q27" s="123"/>
-      <c r="R27" s="123"/>
-      <c r="S27" s="123"/>
-      <c r="T27" s="123"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="123" t="s">
+      <c r="H27" s="117"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="117"/>
+      <c r="L27" s="117"/>
+      <c r="M27" s="117"/>
+      <c r="N27" s="117"/>
+      <c r="O27" s="117"/>
+      <c r="P27" s="117"/>
+      <c r="Q27" s="117"/>
+      <c r="R27" s="117"/>
+      <c r="S27" s="117"/>
+      <c r="T27" s="117"/>
+      <c r="U27" s="118"/>
+      <c r="V27" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="W27" s="123"/>
-      <c r="X27" s="123"/>
-      <c r="Y27" s="123"/>
-      <c r="Z27" s="123"/>
-      <c r="AA27" s="123"/>
-      <c r="AB27" s="123"/>
-      <c r="AC27" s="123"/>
-      <c r="AD27" s="123"/>
-      <c r="AE27" s="123"/>
-      <c r="AF27" s="123"/>
-      <c r="AG27" s="123"/>
-      <c r="AH27" s="123"/>
-      <c r="AI27" s="123"/>
-      <c r="AJ27" s="123"/>
-      <c r="AK27" s="124"/>
+      <c r="W27" s="117"/>
+      <c r="X27" s="117"/>
+      <c r="Y27" s="117"/>
+      <c r="Z27" s="117"/>
+      <c r="AA27" s="117"/>
+      <c r="AB27" s="117"/>
+      <c r="AC27" s="117"/>
+      <c r="AD27" s="117"/>
+      <c r="AE27" s="117"/>
+      <c r="AF27" s="117"/>
+      <c r="AG27" s="117"/>
+      <c r="AH27" s="117"/>
+      <c r="AI27" s="117"/>
+      <c r="AJ27" s="117"/>
+      <c r="AK27" s="119"/>
     </row>
     <row r="28" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="106"/>
-      <c r="B28" s="120" t="s">
+      <c r="A28" s="89"/>
+      <c r="B28" s="108" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="121"/>
-      <c r="D28" s="121"/>
-      <c r="E28" s="121"/>
-      <c r="F28" s="122"/>
-      <c r="G28" s="125" t="s">
+      <c r="C28" s="109"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="116" t="s">
         <v>110</v>
       </c>
-      <c r="H28" s="123"/>
-      <c r="I28" s="123"/>
-      <c r="J28" s="123"/>
-      <c r="K28" s="123"/>
-      <c r="L28" s="123"/>
-      <c r="M28" s="123"/>
-      <c r="N28" s="123"/>
-      <c r="O28" s="123"/>
-      <c r="P28" s="123"/>
-      <c r="Q28" s="123"/>
-      <c r="R28" s="123"/>
-      <c r="S28" s="123"/>
-      <c r="T28" s="123"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="123" t="s">
+      <c r="H28" s="117"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="117"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="117"/>
+      <c r="N28" s="117"/>
+      <c r="O28" s="117"/>
+      <c r="P28" s="117"/>
+      <c r="Q28" s="117"/>
+      <c r="R28" s="117"/>
+      <c r="S28" s="117"/>
+      <c r="T28" s="117"/>
+      <c r="U28" s="118"/>
+      <c r="V28" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="W28" s="123"/>
-      <c r="X28" s="123"/>
-      <c r="Y28" s="123"/>
-      <c r="Z28" s="123"/>
-      <c r="AA28" s="123"/>
-      <c r="AB28" s="123"/>
-      <c r="AC28" s="123"/>
-      <c r="AD28" s="123"/>
-      <c r="AE28" s="123"/>
-      <c r="AF28" s="123"/>
-      <c r="AG28" s="123"/>
-      <c r="AH28" s="123"/>
-      <c r="AI28" s="123"/>
-      <c r="AJ28" s="123"/>
-      <c r="AK28" s="124"/>
+      <c r="W28" s="117"/>
+      <c r="X28" s="117"/>
+      <c r="Y28" s="117"/>
+      <c r="Z28" s="117"/>
+      <c r="AA28" s="117"/>
+      <c r="AB28" s="117"/>
+      <c r="AC28" s="117"/>
+      <c r="AD28" s="117"/>
+      <c r="AE28" s="117"/>
+      <c r="AF28" s="117"/>
+      <c r="AG28" s="117"/>
+      <c r="AH28" s="117"/>
+      <c r="AI28" s="117"/>
+      <c r="AJ28" s="117"/>
+      <c r="AK28" s="119"/>
     </row>
     <row r="29" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="106"/>
-      <c r="B29" s="120" t="s">
+      <c r="A29" s="89"/>
+      <c r="B29" s="108" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="121"/>
-      <c r="D29" s="121"/>
-      <c r="E29" s="121"/>
-      <c r="F29" s="122"/>
-      <c r="G29" s="125" t="s">
+      <c r="C29" s="109"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="116" t="s">
         <v>111</v>
       </c>
-      <c r="H29" s="123"/>
-      <c r="I29" s="123"/>
-      <c r="J29" s="123"/>
-      <c r="K29" s="123"/>
-      <c r="L29" s="123"/>
-      <c r="M29" s="123"/>
-      <c r="N29" s="123"/>
-      <c r="O29" s="123"/>
-      <c r="P29" s="123"/>
-      <c r="Q29" s="123"/>
-      <c r="R29" s="123"/>
-      <c r="S29" s="123"/>
-      <c r="T29" s="123"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="123" t="s">
+      <c r="H29" s="117"/>
+      <c r="I29" s="117"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="117"/>
+      <c r="L29" s="117"/>
+      <c r="M29" s="117"/>
+      <c r="N29" s="117"/>
+      <c r="O29" s="117"/>
+      <c r="P29" s="117"/>
+      <c r="Q29" s="117"/>
+      <c r="R29" s="117"/>
+      <c r="S29" s="117"/>
+      <c r="T29" s="117"/>
+      <c r="U29" s="118"/>
+      <c r="V29" s="117" t="s">
         <v>114</v>
       </c>
-      <c r="W29" s="123"/>
-      <c r="X29" s="123"/>
-      <c r="Y29" s="123"/>
-      <c r="Z29" s="123"/>
-      <c r="AA29" s="123"/>
-      <c r="AB29" s="123"/>
-      <c r="AC29" s="123"/>
-      <c r="AD29" s="123"/>
-      <c r="AE29" s="123"/>
-      <c r="AF29" s="123"/>
-      <c r="AG29" s="123"/>
-      <c r="AH29" s="123"/>
-      <c r="AI29" s="123"/>
-      <c r="AJ29" s="123"/>
-      <c r="AK29" s="124"/>
+      <c r="W29" s="117"/>
+      <c r="X29" s="117"/>
+      <c r="Y29" s="117"/>
+      <c r="Z29" s="117"/>
+      <c r="AA29" s="117"/>
+      <c r="AB29" s="117"/>
+      <c r="AC29" s="117"/>
+      <c r="AD29" s="117"/>
+      <c r="AE29" s="117"/>
+      <c r="AF29" s="117"/>
+      <c r="AG29" s="117"/>
+      <c r="AH29" s="117"/>
+      <c r="AI29" s="117"/>
+      <c r="AJ29" s="117"/>
+      <c r="AK29" s="119"/>
     </row>
     <row r="30" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="106"/>
-      <c r="B30" s="120" t="s">
+      <c r="A30" s="89"/>
+      <c r="B30" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="121"/>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="122"/>
-      <c r="G30" s="125" t="s">
+      <c r="C30" s="109"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="116" t="s">
         <v>113</v>
       </c>
-      <c r="H30" s="123"/>
-      <c r="I30" s="123"/>
-      <c r="J30" s="123"/>
-      <c r="K30" s="123"/>
-      <c r="L30" s="123"/>
-      <c r="M30" s="123"/>
-      <c r="N30" s="123"/>
-      <c r="O30" s="123"/>
-      <c r="P30" s="123"/>
-      <c r="Q30" s="123"/>
-      <c r="R30" s="123"/>
-      <c r="S30" s="123"/>
-      <c r="T30" s="123"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="123" t="s">
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="117"/>
+      <c r="O30" s="117"/>
+      <c r="P30" s="117"/>
+      <c r="Q30" s="117"/>
+      <c r="R30" s="117"/>
+      <c r="S30" s="117"/>
+      <c r="T30" s="117"/>
+      <c r="U30" s="118"/>
+      <c r="V30" s="117" t="s">
         <v>76</v>
       </c>
-      <c r="W30" s="123"/>
-      <c r="X30" s="123"/>
-      <c r="Y30" s="123"/>
-      <c r="Z30" s="123"/>
-      <c r="AA30" s="123"/>
-      <c r="AB30" s="123"/>
-      <c r="AC30" s="123"/>
-      <c r="AD30" s="123"/>
-      <c r="AE30" s="123"/>
-      <c r="AF30" s="123"/>
-      <c r="AG30" s="123"/>
-      <c r="AH30" s="123"/>
-      <c r="AI30" s="123"/>
-      <c r="AJ30" s="123"/>
-      <c r="AK30" s="124"/>
+      <c r="W30" s="117"/>
+      <c r="X30" s="117"/>
+      <c r="Y30" s="117"/>
+      <c r="Z30" s="117"/>
+      <c r="AA30" s="117"/>
+      <c r="AB30" s="117"/>
+      <c r="AC30" s="117"/>
+      <c r="AD30" s="117"/>
+      <c r="AE30" s="117"/>
+      <c r="AF30" s="117"/>
+      <c r="AG30" s="117"/>
+      <c r="AH30" s="117"/>
+      <c r="AI30" s="117"/>
+      <c r="AJ30" s="117"/>
+      <c r="AK30" s="119"/>
     </row>
     <row r="31" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="106"/>
-      <c r="B31" s="120" t="s">
+      <c r="A31" s="89"/>
+      <c r="B31" s="108" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="121"/>
-      <c r="D31" s="121"/>
-      <c r="E31" s="121"/>
-      <c r="F31" s="122"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26" t="s">
+      <c r="C31" s="109"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="123"/>
-      <c r="AC31" s="123"/>
-      <c r="AD31" s="123"/>
-      <c r="AE31" s="123"/>
-      <c r="AF31" s="123"/>
-      <c r="AG31" s="123"/>
-      <c r="AH31" s="123"/>
-      <c r="AI31" s="123"/>
-      <c r="AJ31" s="123"/>
-      <c r="AK31" s="124"/>
+      <c r="I31" s="118"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="118"/>
+      <c r="L31" s="118"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="118"/>
+      <c r="O31" s="118"/>
+      <c r="P31" s="118"/>
+      <c r="Q31" s="118"/>
+      <c r="R31" s="118"/>
+      <c r="S31" s="118"/>
+      <c r="T31" s="118"/>
+      <c r="U31" s="118"/>
+      <c r="V31" s="118"/>
+      <c r="W31" s="118"/>
+      <c r="X31" s="118"/>
+      <c r="Y31" s="118"/>
+      <c r="Z31" s="118"/>
+      <c r="AA31" s="118"/>
+      <c r="AB31" s="117"/>
+      <c r="AC31" s="117"/>
+      <c r="AD31" s="117"/>
+      <c r="AE31" s="117"/>
+      <c r="AF31" s="117"/>
+      <c r="AG31" s="117"/>
+      <c r="AH31" s="117"/>
+      <c r="AI31" s="117"/>
+      <c r="AJ31" s="117"/>
+      <c r="AK31" s="119"/>
     </row>
     <row r="32" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="106"/>
-      <c r="B32" s="120" t="s">
+      <c r="A32" s="89"/>
+      <c r="B32" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="121"/>
-      <c r="E32" s="121"/>
-      <c r="F32" s="122"/>
-      <c r="G32" s="120" t="s">
+      <c r="C32" s="109"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="108" t="s">
         <v>99</v>
       </c>
-      <c r="H32" s="121"/>
-      <c r="I32" s="121"/>
-      <c r="J32" s="121"/>
-      <c r="K32" s="121"/>
-      <c r="L32" s="121"/>
-      <c r="M32" s="156" t="s">
+      <c r="H32" s="109"/>
+      <c r="I32" s="109"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="109"/>
+      <c r="L32" s="109"/>
+      <c r="M32" s="120" t="s">
         <v>115</v>
       </c>
-      <c r="N32" s="123"/>
-      <c r="O32" s="123"/>
-      <c r="P32" s="123"/>
-      <c r="Q32" s="123"/>
-      <c r="R32" s="123"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="26"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="26"/>
-      <c r="Y32" s="26"/>
-      <c r="Z32" s="26"/>
-      <c r="AA32" s="26"/>
-      <c r="AB32" s="26"/>
-      <c r="AC32" s="26"/>
-      <c r="AD32" s="26"/>
-      <c r="AE32" s="26"/>
-      <c r="AF32" s="26"/>
-      <c r="AG32" s="26"/>
-      <c r="AH32" s="26"/>
-      <c r="AI32" s="26"/>
-      <c r="AJ32" s="26"/>
-      <c r="AK32" s="27"/>
+      <c r="N32" s="117"/>
+      <c r="O32" s="117"/>
+      <c r="P32" s="117"/>
+      <c r="Q32" s="117"/>
+      <c r="R32" s="117"/>
+      <c r="S32" s="118"/>
+      <c r="T32" s="118"/>
+      <c r="U32" s="118"/>
+      <c r="V32" s="118"/>
+      <c r="W32" s="118"/>
+      <c r="X32" s="118"/>
+      <c r="Y32" s="118"/>
+      <c r="Z32" s="118"/>
+      <c r="AA32" s="118"/>
+      <c r="AB32" s="118"/>
+      <c r="AC32" s="118"/>
+      <c r="AD32" s="118"/>
+      <c r="AE32" s="118"/>
+      <c r="AF32" s="118"/>
+      <c r="AG32" s="118"/>
+      <c r="AH32" s="118"/>
+      <c r="AI32" s="118"/>
+      <c r="AJ32" s="118"/>
+      <c r="AK32" s="121"/>
     </row>
     <row r="33" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="106"/>
-      <c r="B33" s="120" t="s">
+      <c r="A33" s="89"/>
+      <c r="B33" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="121"/>
-      <c r="D33" s="121"/>
-      <c r="E33" s="121"/>
-      <c r="F33" s="122"/>
-      <c r="G33" s="125" t="s">
+      <c r="C33" s="109"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="110"/>
+      <c r="G33" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="H33" s="123"/>
-      <c r="I33" s="123"/>
-      <c r="J33" s="123"/>
-      <c r="K33" s="123"/>
-      <c r="L33" s="123"/>
-      <c r="M33" s="123"/>
-      <c r="N33" s="123"/>
-      <c r="O33" s="123"/>
-      <c r="P33" s="123"/>
-      <c r="Q33" s="123"/>
-      <c r="R33" s="123"/>
-      <c r="S33" s="123"/>
-      <c r="T33" s="123"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="123" t="s">
+      <c r="H33" s="117"/>
+      <c r="I33" s="117"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="117"/>
+      <c r="N33" s="117"/>
+      <c r="O33" s="117"/>
+      <c r="P33" s="117"/>
+      <c r="Q33" s="117"/>
+      <c r="R33" s="117"/>
+      <c r="S33" s="117"/>
+      <c r="T33" s="117"/>
+      <c r="U33" s="118"/>
+      <c r="V33" s="117" t="s">
         <v>77</v>
       </c>
-      <c r="W33" s="123"/>
-      <c r="X33" s="123"/>
-      <c r="Y33" s="123"/>
-      <c r="Z33" s="123"/>
-      <c r="AA33" s="123"/>
-      <c r="AB33" s="123"/>
-      <c r="AC33" s="123"/>
-      <c r="AD33" s="123"/>
-      <c r="AE33" s="123"/>
-      <c r="AF33" s="123"/>
-      <c r="AG33" s="123"/>
-      <c r="AH33" s="123"/>
-      <c r="AI33" s="123"/>
-      <c r="AJ33" s="123"/>
-      <c r="AK33" s="124"/>
+      <c r="W33" s="117"/>
+      <c r="X33" s="117"/>
+      <c r="Y33" s="117"/>
+      <c r="Z33" s="117"/>
+      <c r="AA33" s="117"/>
+      <c r="AB33" s="117"/>
+      <c r="AC33" s="117"/>
+      <c r="AD33" s="117"/>
+      <c r="AE33" s="117"/>
+      <c r="AF33" s="117"/>
+      <c r="AG33" s="117"/>
+      <c r="AH33" s="117"/>
+      <c r="AI33" s="117"/>
+      <c r="AJ33" s="117"/>
+      <c r="AK33" s="119"/>
     </row>
     <row r="34" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="106"/>
-      <c r="B34" s="120" t="s">
+      <c r="A34" s="89"/>
+      <c r="B34" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="121"/>
-      <c r="D34" s="121"/>
-      <c r="E34" s="121"/>
-      <c r="F34" s="122"/>
-      <c r="G34" s="125"/>
-      <c r="H34" s="123"/>
-      <c r="I34" s="123"/>
-      <c r="J34" s="123"/>
-      <c r="K34" s="123"/>
-      <c r="L34" s="123"/>
-      <c r="M34" s="123"/>
-      <c r="N34" s="123"/>
-      <c r="O34" s="123"/>
-      <c r="P34" s="123"/>
-      <c r="Q34" s="123"/>
-      <c r="R34" s="123"/>
-      <c r="S34" s="123"/>
-      <c r="T34" s="123"/>
-      <c r="U34" s="123"/>
-      <c r="V34" s="123"/>
-      <c r="W34" s="123"/>
-      <c r="X34" s="123"/>
-      <c r="Y34" s="123"/>
-      <c r="Z34" s="123"/>
-      <c r="AA34" s="123"/>
-      <c r="AB34" s="123"/>
-      <c r="AC34" s="123"/>
-      <c r="AD34" s="123"/>
-      <c r="AE34" s="123"/>
-      <c r="AF34" s="123"/>
-      <c r="AG34" s="123"/>
-      <c r="AH34" s="123"/>
-      <c r="AI34" s="123"/>
-      <c r="AJ34" s="123"/>
-      <c r="AK34" s="124"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="110"/>
+      <c r="G34" s="116"/>
+      <c r="H34" s="117"/>
+      <c r="I34" s="117"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="117"/>
+      <c r="L34" s="117"/>
+      <c r="M34" s="117"/>
+      <c r="N34" s="117"/>
+      <c r="O34" s="117"/>
+      <c r="P34" s="117"/>
+      <c r="Q34" s="117"/>
+      <c r="R34" s="117"/>
+      <c r="S34" s="117"/>
+      <c r="T34" s="117"/>
+      <c r="U34" s="117"/>
+      <c r="V34" s="117"/>
+      <c r="W34" s="117"/>
+      <c r="X34" s="117"/>
+      <c r="Y34" s="117"/>
+      <c r="Z34" s="117"/>
+      <c r="AA34" s="117"/>
+      <c r="AB34" s="117"/>
+      <c r="AC34" s="117"/>
+      <c r="AD34" s="117"/>
+      <c r="AE34" s="117"/>
+      <c r="AF34" s="117"/>
+      <c r="AG34" s="117"/>
+      <c r="AH34" s="117"/>
+      <c r="AI34" s="117"/>
+      <c r="AJ34" s="117"/>
+      <c r="AK34" s="119"/>
     </row>
     <row r="35" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="106"/>
-      <c r="B35" s="120" t="s">
+      <c r="A35" s="89"/>
+      <c r="B35" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="121"/>
-      <c r="D35" s="121"/>
-      <c r="E35" s="121"/>
-      <c r="F35" s="122"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26" t="s">
+      <c r="C35" s="109"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="26"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="26"/>
-      <c r="Y35" s="26"/>
-      <c r="Z35" s="26"/>
-      <c r="AA35" s="26"/>
-      <c r="AB35" s="123"/>
-      <c r="AC35" s="123"/>
-      <c r="AD35" s="123"/>
-      <c r="AE35" s="123"/>
-      <c r="AF35" s="123"/>
-      <c r="AG35" s="123"/>
-      <c r="AH35" s="123"/>
-      <c r="AI35" s="123"/>
-      <c r="AJ35" s="123"/>
-      <c r="AK35" s="124"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="118"/>
+      <c r="L35" s="118"/>
+      <c r="M35" s="118"/>
+      <c r="N35" s="118"/>
+      <c r="O35" s="118"/>
+      <c r="P35" s="118"/>
+      <c r="Q35" s="118"/>
+      <c r="R35" s="118"/>
+      <c r="S35" s="118"/>
+      <c r="T35" s="118"/>
+      <c r="U35" s="118"/>
+      <c r="V35" s="118"/>
+      <c r="W35" s="118"/>
+      <c r="X35" s="118"/>
+      <c r="Y35" s="118"/>
+      <c r="Z35" s="118"/>
+      <c r="AA35" s="118"/>
+      <c r="AB35" s="117"/>
+      <c r="AC35" s="117"/>
+      <c r="AD35" s="117"/>
+      <c r="AE35" s="117"/>
+      <c r="AF35" s="117"/>
+      <c r="AG35" s="117"/>
+      <c r="AH35" s="117"/>
+      <c r="AI35" s="117"/>
+      <c r="AJ35" s="117"/>
+      <c r="AK35" s="119"/>
     </row>
     <row r="36" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="106"/>
-      <c r="B36" s="154" t="s">
+      <c r="A36" s="89"/>
+      <c r="B36" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="133"/>
-      <c r="D36" s="133"/>
-      <c r="E36" s="133"/>
-      <c r="F36" s="155"/>
-      <c r="G36" s="28" t="s">
+      <c r="C36" s="123"/>
+      <c r="D36" s="123"/>
+      <c r="E36" s="123"/>
+      <c r="F36" s="124"/>
+      <c r="G36" s="125" t="s">
         <v>89</v>
       </c>
-      <c r="H36" s="29"/>
-      <c r="I36" s="132" t="s">
+      <c r="H36" s="126"/>
+      <c r="I36" s="127" t="s">
         <v>90</v>
       </c>
-      <c r="J36" s="132"/>
-      <c r="K36" s="132"/>
-      <c r="L36" s="132"/>
-      <c r="M36" s="132"/>
-      <c r="N36" s="132"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="133" t="s">
+      <c r="J36" s="127"/>
+      <c r="K36" s="127"/>
+      <c r="L36" s="127"/>
+      <c r="M36" s="127"/>
+      <c r="N36" s="127"/>
+      <c r="O36" s="126"/>
+      <c r="P36" s="123" t="s">
         <v>91</v>
       </c>
-      <c r="Q36" s="133"/>
-      <c r="R36" s="133"/>
-      <c r="S36" s="132" t="s">
+      <c r="Q36" s="123"/>
+      <c r="R36" s="123"/>
+      <c r="S36" s="127" t="s">
         <v>92</v>
       </c>
-      <c r="T36" s="132"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="133" t="s">
+      <c r="T36" s="127"/>
+      <c r="U36" s="126"/>
+      <c r="V36" s="123" t="s">
         <v>93</v>
       </c>
-      <c r="W36" s="133"/>
-      <c r="X36" s="133"/>
-      <c r="Y36" s="133"/>
-      <c r="Z36" s="132" t="s">
+      <c r="W36" s="123"/>
+      <c r="X36" s="123"/>
+      <c r="Y36" s="123"/>
+      <c r="Z36" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="AA36" s="132"/>
-      <c r="AB36" s="132"/>
-      <c r="AC36" s="132"/>
-      <c r="AD36" s="132"/>
-      <c r="AE36" s="132"/>
-      <c r="AF36" s="29"/>
-      <c r="AG36" s="29"/>
-      <c r="AH36" s="29"/>
-      <c r="AI36" s="29"/>
-      <c r="AJ36" s="29"/>
-      <c r="AK36" s="30"/>
+      <c r="AA36" s="127"/>
+      <c r="AB36" s="127"/>
+      <c r="AC36" s="127"/>
+      <c r="AD36" s="127"/>
+      <c r="AE36" s="127"/>
+      <c r="AF36" s="126"/>
+      <c r="AG36" s="126"/>
+      <c r="AH36" s="126"/>
+      <c r="AI36" s="126"/>
+      <c r="AJ36" s="126"/>
+      <c r="AK36" s="128"/>
     </row>
     <row r="37" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="106"/>
-      <c r="B37" s="146" t="s">
+      <c r="A37" s="89"/>
+      <c r="B37" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="147"/>
-      <c r="D37" s="147"/>
-      <c r="E37" s="147"/>
-      <c r="F37" s="147"/>
-      <c r="G37" s="147"/>
-      <c r="H37" s="152" t="s">
+      <c r="C37" s="130"/>
+      <c r="D37" s="130"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="130"/>
+      <c r="H37" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="152"/>
-      <c r="J37" s="152"/>
-      <c r="K37" s="152"/>
-      <c r="L37" s="152"/>
-      <c r="M37" s="152"/>
-      <c r="N37" s="152"/>
-      <c r="O37" s="152"/>
-      <c r="P37" s="152"/>
-      <c r="Q37" s="152"/>
-      <c r="R37" s="152"/>
-      <c r="S37" s="152"/>
-      <c r="T37" s="152"/>
-      <c r="U37" s="152"/>
-      <c r="V37" s="152"/>
-      <c r="W37" s="152"/>
-      <c r="X37" s="152"/>
-      <c r="Y37" s="152"/>
-      <c r="Z37" s="152"/>
-      <c r="AA37" s="152"/>
-      <c r="AB37" s="152"/>
-      <c r="AC37" s="152"/>
-      <c r="AD37" s="152"/>
-      <c r="AE37" s="152"/>
-      <c r="AF37" s="152"/>
-      <c r="AG37" s="152"/>
-      <c r="AH37" s="152"/>
-      <c r="AI37" s="152"/>
-      <c r="AJ37" s="152"/>
-      <c r="AK37" s="153"/>
+      <c r="I37" s="131"/>
+      <c r="J37" s="131"/>
+      <c r="K37" s="131"/>
+      <c r="L37" s="131"/>
+      <c r="M37" s="131"/>
+      <c r="N37" s="131"/>
+      <c r="O37" s="131"/>
+      <c r="P37" s="131"/>
+      <c r="Q37" s="131"/>
+      <c r="R37" s="131"/>
+      <c r="S37" s="131"/>
+      <c r="T37" s="131"/>
+      <c r="U37" s="131"/>
+      <c r="V37" s="131"/>
+      <c r="W37" s="131"/>
+      <c r="X37" s="131"/>
+      <c r="Y37" s="131"/>
+      <c r="Z37" s="131"/>
+      <c r="AA37" s="131"/>
+      <c r="AB37" s="131"/>
+      <c r="AC37" s="131"/>
+      <c r="AD37" s="131"/>
+      <c r="AE37" s="131"/>
+      <c r="AF37" s="131"/>
+      <c r="AG37" s="131"/>
+      <c r="AH37" s="131"/>
+      <c r="AI37" s="131"/>
+      <c r="AJ37" s="131"/>
+      <c r="AK37" s="132"/>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="106"/>
-      <c r="B38" s="148" t="s">
+      <c r="A38" s="89"/>
+      <c r="B38" s="133" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="149"/>
-      <c r="D38" s="149"/>
-      <c r="E38" s="149"/>
-      <c r="F38" s="149"/>
-      <c r="G38" s="149"/>
-      <c r="H38" s="149"/>
-      <c r="I38" s="149"/>
-      <c r="J38" s="149"/>
-      <c r="K38" s="149"/>
-      <c r="L38" s="150"/>
-      <c r="M38" s="150"/>
-      <c r="N38" s="150"/>
-      <c r="O38" s="149"/>
-      <c r="P38" s="149"/>
-      <c r="Q38" s="150"/>
-      <c r="R38" s="150"/>
-      <c r="S38" s="150"/>
-      <c r="T38" s="150"/>
-      <c r="U38" s="149"/>
-      <c r="V38" s="149"/>
-      <c r="W38" s="149"/>
-      <c r="X38" s="149"/>
-      <c r="Y38" s="149"/>
-      <c r="Z38" s="149"/>
-      <c r="AA38" s="149"/>
-      <c r="AB38" s="149"/>
-      <c r="AC38" s="149"/>
-      <c r="AD38" s="149"/>
-      <c r="AE38" s="149"/>
-      <c r="AF38" s="149"/>
-      <c r="AG38" s="149"/>
-      <c r="AH38" s="149"/>
-      <c r="AI38" s="149"/>
-      <c r="AJ38" s="149"/>
-      <c r="AK38" s="151"/>
+      <c r="C38" s="134"/>
+      <c r="D38" s="134"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="134"/>
+      <c r="G38" s="134"/>
+      <c r="H38" s="134"/>
+      <c r="I38" s="134"/>
+      <c r="J38" s="134"/>
+      <c r="K38" s="134"/>
+      <c r="L38" s="135"/>
+      <c r="M38" s="135"/>
+      <c r="N38" s="135"/>
+      <c r="O38" s="134"/>
+      <c r="P38" s="134"/>
+      <c r="Q38" s="135"/>
+      <c r="R38" s="135"/>
+      <c r="S38" s="135"/>
+      <c r="T38" s="135"/>
+      <c r="U38" s="134"/>
+      <c r="V38" s="134"/>
+      <c r="W38" s="134"/>
+      <c r="X38" s="134"/>
+      <c r="Y38" s="134"/>
+      <c r="Z38" s="134"/>
+      <c r="AA38" s="134"/>
+      <c r="AB38" s="134"/>
+      <c r="AC38" s="134"/>
+      <c r="AD38" s="134"/>
+      <c r="AE38" s="134"/>
+      <c r="AF38" s="134"/>
+      <c r="AG38" s="134"/>
+      <c r="AH38" s="134"/>
+      <c r="AI38" s="134"/>
+      <c r="AJ38" s="134"/>
+      <c r="AK38" s="136"/>
     </row>
     <row r="39" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="41" t="s">
+      <c r="A39" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="44" t="s">
+      <c r="B39" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="46"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="59"/>
       <c r="G39" s="49" t="s">
         <v>147</v>
       </c>
       <c r="H39" s="50"/>
       <c r="I39" s="50"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="44" t="s">
+      <c r="J39" s="80"/>
+      <c r="K39" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="46"/>
-      <c r="O39" s="47" t="s">
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="59"/>
+      <c r="O39" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="44" t="s">
+      <c r="P39" s="25"/>
+      <c r="Q39" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="R39" s="45"/>
-      <c r="S39" s="45"/>
-      <c r="T39" s="46"/>
-      <c r="U39" s="52" t="s">
+      <c r="R39" s="58"/>
+      <c r="S39" s="58"/>
+      <c r="T39" s="59"/>
+      <c r="U39" s="83" t="s">
         <v>151</v>
       </c>
-      <c r="V39" s="53"/>
-      <c r="W39" s="53"/>
-      <c r="X39" s="53"/>
-      <c r="Y39" s="53"/>
-      <c r="Z39" s="53"/>
-      <c r="AA39" s="53"/>
-      <c r="AB39" s="53"/>
-      <c r="AC39" s="53"/>
-      <c r="AD39" s="53"/>
-      <c r="AE39" s="53"/>
-      <c r="AF39" s="53"/>
-      <c r="AG39" s="53"/>
-      <c r="AH39" s="53"/>
-      <c r="AI39" s="53"/>
-      <c r="AJ39" s="53"/>
-      <c r="AK39" s="54"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
+      <c r="Z39" s="84"/>
+      <c r="AA39" s="84"/>
+      <c r="AB39" s="84"/>
+      <c r="AC39" s="84"/>
+      <c r="AD39" s="84"/>
+      <c r="AE39" s="84"/>
+      <c r="AF39" s="84"/>
+      <c r="AG39" s="84"/>
+      <c r="AH39" s="84"/>
+      <c r="AI39" s="84"/>
+      <c r="AJ39" s="84"/>
+      <c r="AK39" s="85"/>
     </row>
     <row r="40" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="42"/>
-      <c r="B40" s="44" t="s">
+      <c r="A40" s="86"/>
+      <c r="B40" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="46"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="59"/>
       <c r="G40" s="49" t="s">
         <v>153</v>
       </c>
       <c r="H40" s="50"/>
       <c r="I40" s="50"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="44" t="s">
+      <c r="J40" s="80"/>
+      <c r="K40" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="46"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="59"/>
       <c r="O40" s="49" t="s">
         <v>155</v>
       </c>
@@ -4369,488 +4369,517 @@
       <c r="Q40" s="50"/>
       <c r="R40" s="50"/>
       <c r="S40" s="50"/>
-      <c r="T40" s="51"/>
-      <c r="U40" s="21" t="s">
+      <c r="T40" s="80"/>
+      <c r="U40" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="V40" s="52" t="s">
+      <c r="V40" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="W40" s="53"/>
-      <c r="X40" s="53"/>
-      <c r="Y40" s="53"/>
-      <c r="Z40" s="53"/>
-      <c r="AA40" s="54"/>
-      <c r="AB40" s="44" t="s">
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="84"/>
+      <c r="Z40" s="84"/>
+      <c r="AA40" s="85"/>
+      <c r="AB40" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="AC40" s="45"/>
-      <c r="AD40" s="45"/>
-      <c r="AE40" s="45"/>
-      <c r="AF40" s="46"/>
+      <c r="AC40" s="58"/>
+      <c r="AD40" s="58"/>
+      <c r="AE40" s="58"/>
+      <c r="AF40" s="59"/>
       <c r="AG40" s="50" t="s">
         <v>159</v>
       </c>
       <c r="AH40" s="50"/>
       <c r="AI40" s="50"/>
       <c r="AJ40" s="50"/>
-      <c r="AK40" s="51"/>
+      <c r="AK40" s="80"/>
     </row>
     <row r="41" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="43"/>
-      <c r="B41" s="44" t="s">
+      <c r="A41" s="87"/>
+      <c r="B41" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="46"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="59"/>
       <c r="G41" s="49" t="s">
         <v>161</v>
       </c>
       <c r="H41" s="50"/>
       <c r="I41" s="50"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="44" t="s">
+      <c r="J41" s="80"/>
+      <c r="K41" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="L41" s="45"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="46"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="59"/>
       <c r="O41" s="50" t="s">
         <v>163</v>
       </c>
       <c r="P41" s="50"/>
-      <c r="Q41" s="44" t="s">
+      <c r="Q41" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="R41" s="45"/>
-      <c r="S41" s="45"/>
-      <c r="T41" s="46"/>
-      <c r="U41" s="52" t="s">
+      <c r="R41" s="58"/>
+      <c r="S41" s="58"/>
+      <c r="T41" s="59"/>
+      <c r="U41" s="83" t="s">
         <v>165</v>
       </c>
-      <c r="V41" s="53"/>
-      <c r="W41" s="53"/>
-      <c r="X41" s="53"/>
-      <c r="Y41" s="53"/>
-      <c r="Z41" s="53"/>
-      <c r="AA41" s="53"/>
-      <c r="AB41" s="53"/>
-      <c r="AC41" s="53"/>
-      <c r="AD41" s="53"/>
-      <c r="AE41" s="53"/>
-      <c r="AF41" s="53"/>
-      <c r="AG41" s="53"/>
-      <c r="AH41" s="53"/>
-      <c r="AI41" s="53"/>
-      <c r="AJ41" s="53"/>
-      <c r="AK41" s="54"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="84"/>
+      <c r="Z41" s="84"/>
+      <c r="AA41" s="84"/>
+      <c r="AB41" s="84"/>
+      <c r="AC41" s="84"/>
+      <c r="AD41" s="84"/>
+      <c r="AE41" s="84"/>
+      <c r="AF41" s="84"/>
+      <c r="AG41" s="84"/>
+      <c r="AH41" s="84"/>
+      <c r="AI41" s="84"/>
+      <c r="AJ41" s="84"/>
+      <c r="AK41" s="85"/>
     </row>
     <row r="42" spans="1:37" ht="198" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="140" t="s">
+      <c r="B42" s="137" t="s">
         <v>129</v>
       </c>
-      <c r="C42" s="141"/>
-      <c r="D42" s="141"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="141"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="141"/>
-      <c r="I42" s="141"/>
-      <c r="J42" s="141"/>
-      <c r="K42" s="141"/>
-      <c r="L42" s="141"/>
-      <c r="M42" s="141"/>
-      <c r="N42" s="141"/>
-      <c r="O42" s="141"/>
-      <c r="P42" s="141"/>
-      <c r="Q42" s="141"/>
-      <c r="R42" s="141"/>
-      <c r="S42" s="141"/>
-      <c r="T42" s="141"/>
-      <c r="U42" s="141"/>
-      <c r="V42" s="141"/>
-      <c r="W42" s="141"/>
-      <c r="X42" s="141"/>
-      <c r="Y42" s="141"/>
-      <c r="Z42" s="141"/>
-      <c r="AA42" s="141"/>
-      <c r="AB42" s="141"/>
-      <c r="AC42" s="141"/>
-      <c r="AD42" s="141"/>
-      <c r="AE42" s="141"/>
-      <c r="AF42" s="141"/>
-      <c r="AG42" s="141"/>
-      <c r="AH42" s="141"/>
-      <c r="AI42" s="141"/>
-      <c r="AJ42" s="141"/>
-      <c r="AK42" s="142"/>
+      <c r="C42" s="138"/>
+      <c r="D42" s="138"/>
+      <c r="E42" s="138"/>
+      <c r="F42" s="138"/>
+      <c r="G42" s="138"/>
+      <c r="H42" s="138"/>
+      <c r="I42" s="138"/>
+      <c r="J42" s="138"/>
+      <c r="K42" s="138"/>
+      <c r="L42" s="138"/>
+      <c r="M42" s="138"/>
+      <c r="N42" s="138"/>
+      <c r="O42" s="138"/>
+      <c r="P42" s="138"/>
+      <c r="Q42" s="138"/>
+      <c r="R42" s="138"/>
+      <c r="S42" s="138"/>
+      <c r="T42" s="138"/>
+      <c r="U42" s="138"/>
+      <c r="V42" s="138"/>
+      <c r="W42" s="138"/>
+      <c r="X42" s="138"/>
+      <c r="Y42" s="138"/>
+      <c r="Z42" s="138"/>
+      <c r="AA42" s="138"/>
+      <c r="AB42" s="138"/>
+      <c r="AC42" s="138"/>
+      <c r="AD42" s="138"/>
+      <c r="AE42" s="138"/>
+      <c r="AF42" s="138"/>
+      <c r="AG42" s="138"/>
+      <c r="AH42" s="138"/>
+      <c r="AI42" s="138"/>
+      <c r="AJ42" s="138"/>
+      <c r="AK42" s="139"/>
     </row>
     <row r="43" spans="1:37" ht="71.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="140" t="s">
+      <c r="B43" s="137" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="141"/>
-      <c r="D43" s="141"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="141"/>
-      <c r="G43" s="141"/>
-      <c r="H43" s="141"/>
-      <c r="I43" s="141"/>
-      <c r="J43" s="141"/>
-      <c r="K43" s="141"/>
-      <c r="L43" s="141"/>
-      <c r="M43" s="141"/>
-      <c r="N43" s="141"/>
-      <c r="O43" s="141"/>
-      <c r="P43" s="141"/>
-      <c r="Q43" s="141"/>
-      <c r="R43" s="141"/>
-      <c r="S43" s="141"/>
-      <c r="T43" s="141"/>
-      <c r="U43" s="141"/>
-      <c r="V43" s="141"/>
-      <c r="W43" s="141"/>
-      <c r="X43" s="141"/>
-      <c r="Y43" s="141"/>
-      <c r="Z43" s="141"/>
-      <c r="AA43" s="141"/>
-      <c r="AB43" s="141"/>
-      <c r="AC43" s="141"/>
-      <c r="AD43" s="141"/>
-      <c r="AE43" s="141"/>
-      <c r="AF43" s="141"/>
-      <c r="AG43" s="141"/>
-      <c r="AH43" s="141"/>
-      <c r="AI43" s="141"/>
-      <c r="AJ43" s="141"/>
-      <c r="AK43" s="142"/>
+      <c r="C43" s="138"/>
+      <c r="D43" s="138"/>
+      <c r="E43" s="138"/>
+      <c r="F43" s="138"/>
+      <c r="G43" s="138"/>
+      <c r="H43" s="138"/>
+      <c r="I43" s="138"/>
+      <c r="J43" s="138"/>
+      <c r="K43" s="138"/>
+      <c r="L43" s="138"/>
+      <c r="M43" s="138"/>
+      <c r="N43" s="138"/>
+      <c r="O43" s="138"/>
+      <c r="P43" s="138"/>
+      <c r="Q43" s="138"/>
+      <c r="R43" s="138"/>
+      <c r="S43" s="138"/>
+      <c r="T43" s="138"/>
+      <c r="U43" s="138"/>
+      <c r="V43" s="138"/>
+      <c r="W43" s="138"/>
+      <c r="X43" s="138"/>
+      <c r="Y43" s="138"/>
+      <c r="Z43" s="138"/>
+      <c r="AA43" s="138"/>
+      <c r="AB43" s="138"/>
+      <c r="AC43" s="138"/>
+      <c r="AD43" s="138"/>
+      <c r="AE43" s="138"/>
+      <c r="AF43" s="138"/>
+      <c r="AG43" s="138"/>
+      <c r="AH43" s="138"/>
+      <c r="AI43" s="138"/>
+      <c r="AJ43" s="138"/>
+      <c r="AK43" s="139"/>
     </row>
     <row r="44" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="143" t="s">
+      <c r="A44" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="69"/>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="70"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="70"/>
-      <c r="K44" s="70"/>
-      <c r="L44" s="70"/>
-      <c r="M44" s="70"/>
-      <c r="N44" s="70"/>
-      <c r="O44" s="70"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="71" t="s">
+      <c r="B44" s="14"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="16"/>
+      <c r="Q44" s="16"/>
+      <c r="R44" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="S44" s="72"/>
-      <c r="T44" s="72"/>
-      <c r="U44" s="72"/>
-      <c r="V44" s="72"/>
-      <c r="W44" s="79"/>
-      <c r="X44" s="75" t="s">
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="22"/>
+      <c r="X44" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="Y44" s="62"/>
-      <c r="Z44" s="62"/>
-      <c r="AA44" s="62"/>
-      <c r="AB44" s="62"/>
-      <c r="AC44" s="62"/>
-      <c r="AD44" s="62"/>
-      <c r="AE44" s="62"/>
-      <c r="AF44" s="62"/>
-      <c r="AG44" s="62"/>
-      <c r="AH44" s="18"/>
-      <c r="AI44" s="18"/>
-      <c r="AJ44" s="18"/>
-      <c r="AK44" s="31"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="20"/>
+      <c r="AA44" s="20"/>
+      <c r="AB44" s="20"/>
+      <c r="AC44" s="20"/>
+      <c r="AD44" s="20"/>
+      <c r="AE44" s="20"/>
+      <c r="AF44" s="20"/>
+      <c r="AG44" s="20"/>
+      <c r="AH44" s="53"/>
+      <c r="AI44" s="53"/>
+      <c r="AJ44" s="53"/>
+      <c r="AK44" s="141"/>
     </row>
     <row r="45" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144"/>
-      <c r="B45" s="145" t="s">
+      <c r="A45" s="142"/>
+      <c r="B45" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="85"/>
-      <c r="D45" s="85"/>
-      <c r="E45" s="85"/>
-      <c r="F45" s="85"/>
-      <c r="G45" s="85"/>
-      <c r="H45" s="85"/>
-      <c r="I45" s="85"/>
-      <c r="J45" s="85"/>
-      <c r="K45" s="85"/>
-      <c r="L45" s="85"/>
-      <c r="M45" s="85"/>
-      <c r="N45" s="85"/>
-      <c r="O45" s="85"/>
-      <c r="P45" s="32" t="s">
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="73"/>
-      <c r="S45" s="74"/>
-      <c r="T45" s="74"/>
-      <c r="U45" s="74"/>
-      <c r="V45" s="74"/>
-      <c r="W45" s="80"/>
-      <c r="X45" s="76"/>
-      <c r="Y45" s="77"/>
-      <c r="Z45" s="77"/>
-      <c r="AA45" s="77"/>
-      <c r="AB45" s="77"/>
-      <c r="AC45" s="77"/>
-      <c r="AD45" s="77"/>
-      <c r="AE45" s="77"/>
-      <c r="AF45" s="77"/>
-      <c r="AG45" s="77"/>
-      <c r="AH45" s="34"/>
-      <c r="AI45" s="34"/>
-      <c r="AJ45" s="34"/>
-      <c r="AK45" s="35"/>
+      <c r="Q45" s="145"/>
+      <c r="R45" s="30"/>
+      <c r="S45" s="31"/>
+      <c r="T45" s="31"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="31"/>
+      <c r="W45" s="34"/>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="33"/>
+      <c r="Z45" s="33"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="33"/>
+      <c r="AC45" s="33"/>
+      <c r="AD45" s="33"/>
+      <c r="AE45" s="33"/>
+      <c r="AF45" s="33"/>
+      <c r="AG45" s="33"/>
+      <c r="AH45" s="146"/>
+      <c r="AI45" s="146"/>
+      <c r="AJ45" s="146"/>
+      <c r="AK45" s="147"/>
     </row>
     <row r="46" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144"/>
-      <c r="B46" s="59" t="s">
+      <c r="A46" s="142"/>
+      <c r="B46" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="60"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="12" t="s">
+      <c r="C46" s="46"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F46" s="63" t="s">
+      <c r="F46" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="G46" s="63"/>
-      <c r="H46" s="63"/>
-      <c r="I46" s="63"/>
-      <c r="J46" s="63" t="s">
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="K46" s="63"/>
-      <c r="L46" s="63"/>
-      <c r="M46" s="63"/>
-      <c r="N46" s="63"/>
-      <c r="O46" s="63"/>
-      <c r="P46" s="63"/>
-      <c r="Q46" s="63"/>
-      <c r="R46" s="63"/>
-      <c r="S46" s="63"/>
-      <c r="T46" s="63"/>
-      <c r="U46" s="63"/>
-      <c r="V46" s="63"/>
-      <c r="W46" s="63"/>
-      <c r="X46" s="63"/>
-      <c r="Y46" s="63"/>
-      <c r="Z46" s="63"/>
-      <c r="AA46" s="63"/>
-      <c r="AB46" s="63"/>
-      <c r="AC46" s="63"/>
-      <c r="AD46" s="63"/>
-      <c r="AE46" s="63"/>
-      <c r="AF46" s="63"/>
-      <c r="AG46" s="63"/>
-      <c r="AH46" s="63"/>
-      <c r="AI46" s="63"/>
-      <c r="AJ46" s="63"/>
-      <c r="AK46" s="64"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="41"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="41"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="41"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="41"/>
+      <c r="U46" s="41"/>
+      <c r="V46" s="41"/>
+      <c r="W46" s="41"/>
+      <c r="X46" s="41"/>
+      <c r="Y46" s="41"/>
+      <c r="Z46" s="41"/>
+      <c r="AA46" s="41"/>
+      <c r="AB46" s="41"/>
+      <c r="AC46" s="41"/>
+      <c r="AD46" s="41"/>
+      <c r="AE46" s="41"/>
+      <c r="AF46" s="41"/>
+      <c r="AG46" s="41"/>
+      <c r="AH46" s="41"/>
+      <c r="AI46" s="41"/>
+      <c r="AJ46" s="41"/>
+      <c r="AK46" s="42"/>
     </row>
     <row r="47" spans="1:37" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144"/>
-      <c r="B47" s="59" t="s">
+      <c r="A47" s="142"/>
+      <c r="B47" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="59" t="s">
+      <c r="C47" s="46"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="60"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="56" t="s">
+      <c r="F47" s="46"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="I47" s="57"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="57"/>
-      <c r="L47" s="57"/>
-      <c r="M47" s="57"/>
-      <c r="N47" s="57"/>
-      <c r="O47" s="57"/>
-      <c r="P47" s="57"/>
-      <c r="Q47" s="58"/>
-      <c r="R47" s="59" t="s">
+      <c r="I47" s="40"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
+      <c r="M47" s="40"/>
+      <c r="N47" s="40"/>
+      <c r="O47" s="40"/>
+      <c r="P47" s="40"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="S47" s="60"/>
-      <c r="T47" s="61"/>
-      <c r="U47" s="56" t="s">
+      <c r="S47" s="46"/>
+      <c r="T47" s="47"/>
+      <c r="U47" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="V47" s="57"/>
-      <c r="W47" s="57"/>
-      <c r="X47" s="57"/>
-      <c r="Y47" s="57"/>
-      <c r="Z47" s="57"/>
-      <c r="AA47" s="57"/>
-      <c r="AB47" s="57"/>
-      <c r="AC47" s="57"/>
-      <c r="AD47" s="57"/>
-      <c r="AE47" s="13"/>
-      <c r="AF47" s="13"/>
-      <c r="AG47" s="13"/>
-      <c r="AH47" s="13"/>
-      <c r="AI47" s="13"/>
-      <c r="AJ47" s="13"/>
-      <c r="AK47" s="14"/>
+      <c r="V47" s="40"/>
+      <c r="W47" s="40"/>
+      <c r="X47" s="40"/>
+      <c r="Y47" s="40"/>
+      <c r="Z47" s="40"/>
+      <c r="AA47" s="40"/>
+      <c r="AB47" s="40"/>
+      <c r="AC47" s="40"/>
+      <c r="AD47" s="40"/>
+      <c r="AE47" s="148"/>
+      <c r="AF47" s="148"/>
+      <c r="AG47" s="148"/>
+      <c r="AH47" s="148"/>
+      <c r="AI47" s="148"/>
+      <c r="AJ47" s="148"/>
+      <c r="AK47" s="149"/>
     </row>
     <row r="48" spans="1:37" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A48" s="144"/>
-      <c r="B48" s="71" t="s">
+      <c r="A48" s="142"/>
+      <c r="B48" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="72"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="134" t="s">
+      <c r="C48" s="18"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="150" t="s">
         <v>83</v>
       </c>
-      <c r="F48" s="135"/>
-      <c r="G48" s="135"/>
-      <c r="H48" s="135"/>
-      <c r="I48" s="135"/>
-      <c r="J48" s="135"/>
-      <c r="K48" s="135"/>
-      <c r="L48" s="135"/>
-      <c r="M48" s="135"/>
-      <c r="N48" s="135"/>
-      <c r="O48" s="135"/>
-      <c r="P48" s="135"/>
-      <c r="Q48" s="135"/>
-      <c r="R48" s="135"/>
-      <c r="S48" s="135"/>
-      <c r="T48" s="135"/>
-      <c r="U48" s="135"/>
-      <c r="V48" s="135"/>
-      <c r="W48" s="135"/>
-      <c r="X48" s="135"/>
-      <c r="Y48" s="135"/>
-      <c r="Z48" s="135"/>
-      <c r="AA48" s="135"/>
-      <c r="AB48" s="135"/>
-      <c r="AC48" s="135"/>
-      <c r="AD48" s="135"/>
-      <c r="AE48" s="135"/>
-      <c r="AF48" s="135"/>
-      <c r="AG48" s="135"/>
-      <c r="AH48" s="135"/>
-      <c r="AI48" s="135"/>
-      <c r="AJ48" s="135"/>
-      <c r="AK48" s="136"/>
+      <c r="F48" s="151"/>
+      <c r="G48" s="151"/>
+      <c r="H48" s="151"/>
+      <c r="I48" s="151"/>
+      <c r="J48" s="151"/>
+      <c r="K48" s="151"/>
+      <c r="L48" s="151"/>
+      <c r="M48" s="151"/>
+      <c r="N48" s="151"/>
+      <c r="O48" s="151"/>
+      <c r="P48" s="151"/>
+      <c r="Q48" s="151"/>
+      <c r="R48" s="151"/>
+      <c r="S48" s="151"/>
+      <c r="T48" s="151"/>
+      <c r="U48" s="151"/>
+      <c r="V48" s="151"/>
+      <c r="W48" s="151"/>
+      <c r="X48" s="151"/>
+      <c r="Y48" s="151"/>
+      <c r="Z48" s="151"/>
+      <c r="AA48" s="151"/>
+      <c r="AB48" s="151"/>
+      <c r="AC48" s="151"/>
+      <c r="AD48" s="151"/>
+      <c r="AE48" s="151"/>
+      <c r="AF48" s="151"/>
+      <c r="AG48" s="151"/>
+      <c r="AH48" s="151"/>
+      <c r="AI48" s="151"/>
+      <c r="AJ48" s="151"/>
+      <c r="AK48" s="152"/>
     </row>
     <row r="49" spans="1:37" ht="59.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="137" t="s">
+      <c r="B49" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="C49" s="138"/>
-      <c r="D49" s="138"/>
-      <c r="E49" s="138"/>
-      <c r="F49" s="138"/>
-      <c r="G49" s="138"/>
-      <c r="H49" s="138"/>
-      <c r="I49" s="138"/>
-      <c r="J49" s="138"/>
-      <c r="K49" s="138"/>
-      <c r="L49" s="138"/>
-      <c r="M49" s="138"/>
-      <c r="N49" s="138"/>
-      <c r="O49" s="138"/>
-      <c r="P49" s="138"/>
-      <c r="Q49" s="138"/>
-      <c r="R49" s="138"/>
-      <c r="S49" s="138"/>
-      <c r="T49" s="138"/>
-      <c r="U49" s="138"/>
-      <c r="V49" s="138"/>
-      <c r="W49" s="138"/>
-      <c r="X49" s="138"/>
-      <c r="Y49" s="138"/>
-      <c r="Z49" s="138"/>
-      <c r="AA49" s="138"/>
-      <c r="AB49" s="138"/>
-      <c r="AC49" s="138"/>
-      <c r="AD49" s="138"/>
-      <c r="AE49" s="138"/>
-      <c r="AF49" s="138"/>
-      <c r="AG49" s="138"/>
-      <c r="AH49" s="138"/>
-      <c r="AI49" s="138"/>
-      <c r="AJ49" s="138"/>
-      <c r="AK49" s="139"/>
+      <c r="C49" s="155"/>
+      <c r="D49" s="155"/>
+      <c r="E49" s="155"/>
+      <c r="F49" s="155"/>
+      <c r="G49" s="155"/>
+      <c r="H49" s="155"/>
+      <c r="I49" s="155"/>
+      <c r="J49" s="155"/>
+      <c r="K49" s="155"/>
+      <c r="L49" s="155"/>
+      <c r="M49" s="155"/>
+      <c r="N49" s="155"/>
+      <c r="O49" s="155"/>
+      <c r="P49" s="155"/>
+      <c r="Q49" s="155"/>
+      <c r="R49" s="155"/>
+      <c r="S49" s="155"/>
+      <c r="T49" s="155"/>
+      <c r="U49" s="155"/>
+      <c r="V49" s="155"/>
+      <c r="W49" s="155"/>
+      <c r="X49" s="155"/>
+      <c r="Y49" s="155"/>
+      <c r="Z49" s="155"/>
+      <c r="AA49" s="155"/>
+      <c r="AB49" s="155"/>
+      <c r="AC49" s="155"/>
+      <c r="AD49" s="155"/>
+      <c r="AE49" s="155"/>
+      <c r="AF49" s="155"/>
+      <c r="AG49" s="155"/>
+      <c r="AH49" s="155"/>
+      <c r="AI49" s="155"/>
+      <c r="AJ49" s="155"/>
+      <c r="AK49" s="156"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="158">
-    <mergeCell ref="V29:AK29"/>
-    <mergeCell ref="B9:Q9"/>
-    <mergeCell ref="U9:AK9"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B38:AK38"/>
-    <mergeCell ref="Q41:T41"/>
-    <mergeCell ref="U41:AK41"/>
-    <mergeCell ref="AG40:AK40"/>
-    <mergeCell ref="B42:AK42"/>
-    <mergeCell ref="H37:AK37"/>
-    <mergeCell ref="G25:P25"/>
-    <mergeCell ref="S25:AK25"/>
-    <mergeCell ref="G27:T27"/>
-    <mergeCell ref="V27:AK27"/>
-    <mergeCell ref="G28:T28"/>
-    <mergeCell ref="V28:AK28"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G34:AK34"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G29:T29"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="M32:R32"/>
-    <mergeCell ref="I36:N36"/>
-    <mergeCell ref="P36:R36"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="AB35:AK35"/>
-    <mergeCell ref="V33:AK33"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:AK48"/>
-    <mergeCell ref="B49:AK49"/>
-    <mergeCell ref="B43:AK43"/>
-    <mergeCell ref="A44:A48"/>
-    <mergeCell ref="B44:O44"/>
-    <mergeCell ref="R44:W45"/>
-    <mergeCell ref="X44:AG45"/>
-    <mergeCell ref="B45:O45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="J46:AK46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="H47:Q47"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="U47:AD47"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:T39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="O40:T40"/>
+    <mergeCell ref="V40:AA40"/>
+    <mergeCell ref="AB40:AF40"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="K41:N41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="U39:AK39"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="G8:AK8"/>
+    <mergeCell ref="Y10:AK10"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="U18:AK18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="G20:AK20"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:AK19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="B6:O6"/>
+    <mergeCell ref="R6:T7"/>
+    <mergeCell ref="U6:W7"/>
+    <mergeCell ref="X6:Z7"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="Y2:AA2"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="B3:AK3"/>
+    <mergeCell ref="B7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="B4:AK4"/>
+    <mergeCell ref="B5:AK5"/>
+    <mergeCell ref="AA6:AK7"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:AK11"/>
+    <mergeCell ref="AB12:AH12"/>
+    <mergeCell ref="AI12:AK12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:AK14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:Y15"/>
+    <mergeCell ref="Z15:AC15"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="X12:AA12"/>
+    <mergeCell ref="P12:W12"/>
+    <mergeCell ref="AD15:AK15"/>
+    <mergeCell ref="B13:AK13"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="G21:M21"/>
+    <mergeCell ref="Z21:AE21"/>
     <mergeCell ref="A23:A38"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B25:F25"/>
@@ -4875,6 +4904,51 @@
     <mergeCell ref="V36:Y36"/>
     <mergeCell ref="Z36:AE36"/>
     <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:AK48"/>
+    <mergeCell ref="B49:AK49"/>
+    <mergeCell ref="B43:AK43"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="B44:O44"/>
+    <mergeCell ref="R44:W45"/>
+    <mergeCell ref="X44:AG45"/>
+    <mergeCell ref="B45:O45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="J46:AK46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="H47:Q47"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="U47:AD47"/>
+    <mergeCell ref="B42:AK42"/>
+    <mergeCell ref="H37:AK37"/>
+    <mergeCell ref="G25:P25"/>
+    <mergeCell ref="S25:AK25"/>
+    <mergeCell ref="G27:T27"/>
+    <mergeCell ref="V27:AK27"/>
+    <mergeCell ref="G28:T28"/>
+    <mergeCell ref="V28:AK28"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:AK34"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G29:T29"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="M32:R32"/>
+    <mergeCell ref="I36:N36"/>
+    <mergeCell ref="P36:R36"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="AB35:AK35"/>
+    <mergeCell ref="V33:AK33"/>
+    <mergeCell ref="V29:AK29"/>
+    <mergeCell ref="B9:Q9"/>
+    <mergeCell ref="U9:AK9"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:AK38"/>
+    <mergeCell ref="Q41:T41"/>
+    <mergeCell ref="U41:AK41"/>
+    <mergeCell ref="AG40:AK40"/>
     <mergeCell ref="AF21:AJ21"/>
     <mergeCell ref="AF22:AJ22"/>
     <mergeCell ref="Q22:AB22"/>
@@ -4887,83 +4961,9 @@
     <mergeCell ref="G18:I18"/>
     <mergeCell ref="J18:N18"/>
     <mergeCell ref="O18:P18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="G21:M21"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:AK11"/>
-    <mergeCell ref="AB12:AH12"/>
-    <mergeCell ref="AI12:AK12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:AK14"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:Y15"/>
-    <mergeCell ref="Z15:AC15"/>
-    <mergeCell ref="L12:O12"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="X12:AA12"/>
-    <mergeCell ref="P12:W12"/>
-    <mergeCell ref="AD15:AK15"/>
-    <mergeCell ref="B13:AK13"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="B6:O6"/>
-    <mergeCell ref="R6:T7"/>
-    <mergeCell ref="U6:W7"/>
-    <mergeCell ref="X6:Z7"/>
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="Y2:AA2"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="B3:AK3"/>
-    <mergeCell ref="B7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="B4:AK4"/>
-    <mergeCell ref="B5:AK5"/>
-    <mergeCell ref="AA6:AK7"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="H10:I10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="G8:AK8"/>
-    <mergeCell ref="Y10:AK10"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="U18:AK18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="G20:AK20"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:AK19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:T39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="O40:T40"/>
-    <mergeCell ref="V40:AA40"/>
-    <mergeCell ref="AB40:AF40"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="K41:N41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G40:J40"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="U39:AK39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
